--- a/sheets/조재수대금교본/검수/신고산 타령.xlsx
+++ b/sheets/조재수대금교본/검수/신고산 타령.xlsx
@@ -4588,9 +4588,9 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 △
-潢⌝</t>
+潢</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4610,7 +4610,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -4657,7 +4657,6 @@
         <is>
           <t xml:space="preserve">△
 㴌
-⌝
 –</t>
         </is>
       </c>
@@ -4695,9 +4694,9 @@
       <c r="E5" s="23"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌⌝
+          <t xml:space="preserve">㴌
 △
-㴌⌝</t>
+㴌</t>
         </is>
       </c>
       <c r="G5" s="23"/>
@@ -4707,9 +4706,9 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 △
-潢⌝</t>
+潢</t>
         </is>
       </c>
       <c r="M5" s="23"/>
@@ -4724,7 +4723,6 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-⌝
 △
 潢</t>
         </is>
@@ -4745,16 +4743,11 @@
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
@@ -4770,7 +4763,6 @@
         <is>
           <t xml:space="preserve">△
 汰
-⌝
 潢</t>
         </is>
       </c>
@@ -4787,10 +4779,8 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌝
-△
+          <t xml:space="preserve">△
 汰
-⌝
 潢</t>
         </is>
       </c>
@@ -4918,10 +4908,9 @@
       <c r="E9" s="23"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⌝
+          <t xml:space="preserve">潢
 △
-汰
-⌝</t>
+汰</t>
         </is>
       </c>
       <c r="G9" s="23"/>
@@ -4939,9 +4928,9 @@
       <c r="M9" s="23"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌝
+          <t xml:space="preserve">淋
 㴌
-㴌⌝</t>
+㴌</t>
         </is>
       </c>
       <c r="O9" s="23"/>
@@ -4958,10 +4947,8 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-⌝
 㴌
-㴌
-⌝</t>
+㴌</t>
         </is>
       </c>
       <c r="U9" s="23"/>
@@ -4978,11 +4965,7 @@
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -4996,17 +4979,15 @@
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌⌝
-–
-‹</t>
+㴌
+–</t>
         </is>
       </c>
       <c r="O10" s="24"/>
@@ -5014,17 +4995,15 @@
       <c r="Q10" s="24"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S10" s="24"/>
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌⌝
-–
-‹</t>
+㴌
+–</t>
         </is>
       </c>
       <c r="U10" s="24"/>
@@ -5051,9 +5030,9 @@
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌⌝
+          <t xml:space="preserve">㴌
 △
-湳⌝</t>
+湳</t>
         </is>
       </c>
       <c r="I11" s="22"/>
@@ -5164,7 +5143,6 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-⌝
 △
 潢</t>
         </is>
@@ -5172,9 +5150,9 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌⌝
+          <t xml:space="preserve">㴌
 △
-淋⌝</t>
+淋</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -5219,18 +5197,12 @@
     </row>
     <row r="14" ht="144.45" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌝
-△
+          <t xml:space="preserve">△
 汰
-⌝
 潢</t>
         </is>
       </c>
@@ -5239,8 +5211,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -5260,8 +5231,7 @@
         <is>
           <t xml:space="preserve">南
 –
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="O14" s="24"/>
@@ -5323,9 +5293,8 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-⌝
 南
-林⌝</t>
+林</t>
         </is>
       </c>
       <c r="O15" s="22"/>
@@ -5342,9 +5311,8 @@
       <c r="T15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-⌝
 南
-林⌝</t>
+林</t>
         </is>
       </c>
       <c r="U15" s="22"/>
@@ -5379,7 +5347,6 @@
         <is>
           <t xml:space="preserve">△
 姑
-⌝
 △</t>
         </is>
       </c>
@@ -5397,7 +5364,7 @@
       <c r="T16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-姑⌝
+姑
 △</t>
         </is>
       </c>
@@ -5424,9 +5391,8 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-⌝
 △
-潢⌝</t>
+潢</t>
         </is>
       </c>
       <c r="M17" s="23"/>
@@ -5442,9 +5408,9 @@
       <c r="Q17" s="23"/>
       <c r="R17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 △
-潢⌝</t>
+潢</t>
         </is>
       </c>
       <c r="S17" s="23"/>
@@ -5463,8 +5429,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="E18" s="24"/>
@@ -5490,7 +5455,6 @@
         <is>
           <t xml:space="preserve">△
 汰
-⌝
 潢</t>
         </is>
       </c>
@@ -5509,7 +5473,6 @@
         <is>
           <t xml:space="preserve">△
 汰
-⌝
 潢</t>
         </is>
       </c>
@@ -5642,11 +5605,7 @@
       <c r="Q24" s="24"/>
       <c r="R24" s="21"/>
       <c r="S24" s="24"/>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
     <row r="25" ht="144.45" customHeight="true">
@@ -5671,7 +5630,7 @@
       <c r="S25" s="22"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="U25" s="22"/>

--- a/sheets/조재수대금교본/검수/신고산 타령.xlsx
+++ b/sheets/조재수대금교본/검수/신고산 타령.xlsx
@@ -4588,9 +4588,9 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 △
-潢</t>
+潢⌝</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -4610,7 +4610,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="U3" s="22"/>
@@ -4657,6 +4657,7 @@
         <is>
           <t xml:space="preserve">△
 㴌
+⌝
 –</t>
         </is>
       </c>
@@ -4694,9 +4695,9 @@
       <c r="E5" s="23"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌⌝
 △
-㴌</t>
+㴌⌝</t>
         </is>
       </c>
       <c r="G5" s="23"/>
@@ -4706,9 +4707,9 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 △
-潢</t>
+潢⌝</t>
         </is>
       </c>
       <c r="M5" s="23"/>
@@ -4723,6 +4724,7 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+⌝
 △
 潢</t>
         </is>
@@ -4763,6 +4765,7 @@
         <is>
           <t xml:space="preserve">△
 汰
+⌝
 潢</t>
         </is>
       </c>
@@ -4779,8 +4782,10 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
+          <t xml:space="preserve">⌝
+△
 汰
+⌝
 潢</t>
         </is>
       </c>
@@ -4908,9 +4913,10 @@
       <c r="E9" s="23"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢⌝
 △
-汰</t>
+汰
+⌝</t>
         </is>
       </c>
       <c r="G9" s="23"/>
@@ -4928,9 +4934,9 @@
       <c r="M9" s="23"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋⌝
 㴌
-㴌</t>
+㴌⌝</t>
         </is>
       </c>
       <c r="O9" s="23"/>
@@ -4947,8 +4953,10 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
+⌝
 㴌
-㴌</t>
+㴌
+⌝</t>
         </is>
       </c>
       <c r="U9" s="23"/>
@@ -4986,7 +4994,7 @@
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
+㴌⌝
 –</t>
         </is>
       </c>
@@ -5002,7 +5010,7 @@
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
+㴌⌝
 –</t>
         </is>
       </c>
@@ -5030,9 +5038,9 @@
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌⌝
 △
-湳</t>
+湳⌝</t>
         </is>
       </c>
       <c r="I11" s="22"/>
@@ -5143,6 +5151,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+⌝
 △
 潢</t>
         </is>
@@ -5150,9 +5159,9 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌⌝
 △
-淋</t>
+淋⌝</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -5201,8 +5210,10 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
+          <t xml:space="preserve">⌝
+△
 汰
+⌝
 潢</t>
         </is>
       </c>
@@ -5293,8 +5304,9 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+⌝
 南
-林</t>
+林⌝</t>
         </is>
       </c>
       <c r="O15" s="22"/>
@@ -5311,8 +5323,9 @@
       <c r="T15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+⌝
 南
-林</t>
+林⌝</t>
         </is>
       </c>
       <c r="U15" s="22"/>
@@ -5347,6 +5360,7 @@
         <is>
           <t xml:space="preserve">△
 姑
+⌝
 △</t>
         </is>
       </c>
@@ -5364,7 +5378,7 @@
       <c r="T16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-姑
+姑⌝
 △</t>
         </is>
       </c>
@@ -5391,8 +5405,9 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+⌝
 △
-潢</t>
+潢⌝</t>
         </is>
       </c>
       <c r="M17" s="23"/>
@@ -5408,9 +5423,9 @@
       <c r="Q17" s="23"/>
       <c r="R17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 △
-潢</t>
+潢⌝</t>
         </is>
       </c>
       <c r="S17" s="23"/>
@@ -5455,6 +5470,7 @@
         <is>
           <t xml:space="preserve">△
 汰
+⌝
 潢</t>
         </is>
       </c>
@@ -5473,6 +5489,7 @@
         <is>
           <t xml:space="preserve">△
 汰
+⌝
 潢</t>
         </is>
       </c>
@@ -5630,7 +5647,7 @@
       <c r="S25" s="22"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="U25" s="22"/>

--- a/sheets/조재수대금교본/검수/신고산 타령.xlsx
+++ b/sheets/조재수대금교본/검수/신고산 타령.xlsx
@@ -4486,25 +4486,25 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
